--- a/GameDatas/AttributeSet/AttributeExcel.xlsx
+++ b/GameDatas/AttributeSet/AttributeExcel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="3645" windowWidth="28800" windowHeight="13110" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="AttributeData" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -33,13 +33,6 @@
       <family val="3"/>
       <sz val="8"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -108,16 +101,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -489,37 +479,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>AttributeSetName</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>AttributeName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>BaseValue</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>MinValue</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>MaxValue</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>DerivedAttributeInfo</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>bCanStack</t>
         </is>
@@ -960,37 +950,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>AttributeSetName</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>AttributeName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>BaseValue</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>MinValue</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>MaxValue</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>DerivedAttributeInfo</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>bCanStack</t>
         </is>
@@ -1133,7 +1123,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1158,7 +1148,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1236,37 +1226,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>AttributeSetName</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>AttributeName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>BaseValue</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>MinValue</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>MaxValue</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>DerivedAttributeInfo</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>bCanStack</t>
         </is>
@@ -1409,7 +1399,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1434,7 +1424,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1509,13 +1499,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="b">
@@ -1534,13 +1524,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="b">

--- a/GameDatas/AttributeSet/AttributeExcel.xlsx
+++ b/GameDatas/AttributeSet/AttributeExcel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="3645" windowWidth="28800" windowHeight="13110" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="AttributeData" sheetId="1" state="visible" r:id="rId1"/>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>

--- a/GameDatas/AttributeSet/AttributeExcel.xlsx
+++ b/GameDatas/AttributeSet/AttributeExcel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.305.56234"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="AttributeData" sheetId="1" r:id="rId1"/>
@@ -1815,7 +1815,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="0">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="0">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="0">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D7" s="0">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="0">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D8" s="0">
         <v>0</v>
